--- a/sources/jin_step6.xlsx
+++ b/sources/jin_step6.xlsx
@@ -821,6 +821,11 @@
           <t>System</t>
         </is>
       </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>8a32a40c-eb99-4c3e-83d9-8fb9cb6f62c4</t>
+        </is>
+      </c>
       <c r="Q8" t="inlineStr">
         <is>
           <t>8a32a40c-eb99-4c3e-83d9-8fb9cb6f62c4</t>
@@ -858,6 +863,11 @@
           <t>System</t>
         </is>
       </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>9b654aae-43b4-4ee3-835c-083e97efa144</t>
+        </is>
+      </c>
       <c r="Q9" t="inlineStr">
         <is>
           <t>9b654aae-43b4-4ee3-835c-083e97efa144</t>
@@ -900,6 +910,11 @@
           <t>System</t>
         </is>
       </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>7cbf5cdd-f696-407b-bc8d-f553aec297ca</t>
+        </is>
+      </c>
       <c r="Q10" t="inlineStr">
         <is>
           <t>7cbf5cdd-f696-407b-bc8d-f553aec297ca</t>
@@ -942,6 +957,11 @@
           <t>System</t>
         </is>
       </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>9c909692-e175-413c-bb3d-d48e4dbe578e</t>
+        </is>
+      </c>
       <c r="Q11" t="inlineStr">
         <is>
           <t>9c909692-e175-413c-bb3d-d48e4dbe578e</t>
@@ -984,6 +1004,11 @@
           <t>System</t>
         </is>
       </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>767ed810-48c3-4120-acc7-99c5a2660fcb</t>
+        </is>
+      </c>
       <c r="Q12" t="inlineStr">
         <is>
           <t>767ed810-48c3-4120-acc7-99c5a2660fcb</t>
@@ -1026,6 +1051,11 @@
           <t>System</t>
         </is>
       </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>cda82971-a307-467e-ad05-57768181324c</t>
+        </is>
+      </c>
       <c r="Q13" t="inlineStr">
         <is>
           <t>cda82971-a307-467e-ad05-57768181324c</t>
@@ -1078,6 +1108,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>823249d7-37de-46b1-879b-61503eaa94c3</t>
+        </is>
+      </c>
       <c r="Q14" t="inlineStr">
         <is>
           <t>823249d7-37de-46b1-879b-61503eaa94c3</t>
@@ -1125,6 +1160,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>25dd8959-e3d5-46b4-9df3-7e812375a7d4</t>
+        </is>
+      </c>
       <c r="Q15" t="inlineStr">
         <is>
           <t>25dd8959-e3d5-46b4-9df3-7e812375a7d4</t>
@@ -1170,6 +1210,11 @@
       <c r="M16" t="inlineStr">
         <is>
           <t>None</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>67cda8df-b3c2-4b5d-83b0-595685761a80</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
@@ -7223,6 +7268,11 @@
           <t>hhhLmmlhhmm</t>
         </is>
       </c>
+      <c r="P129" t="inlineStr">
+        <is>
+          <t>e55b194e-268a-481a-a9dc-9ef72e09f8d5</t>
+        </is>
+      </c>
       <c r="Q129" t="inlineStr">
         <is>
           <t>e55b194e-268a-481a-a9dc-9ef72e09f8d5</t>
@@ -7255,6 +7305,11 @@
           <t>hhhLmmlhhmL</t>
         </is>
       </c>
+      <c r="P130" t="inlineStr">
+        <is>
+          <t>cb475c41-e8b6-4ff9-bd8e-37a458e72cd2</t>
+        </is>
+      </c>
       <c r="Q130" t="inlineStr">
         <is>
           <t>cb475c41-e8b6-4ff9-bd8e-37a458e72cd2</t>
@@ -7287,6 +7342,11 @@
           <t>hhhLmmlhhlh</t>
         </is>
       </c>
+      <c r="P131" t="inlineStr">
+        <is>
+          <t>d026b17f-948b-4d7e-aeb1-e5f6517e00b6</t>
+        </is>
+      </c>
       <c r="Q131" t="inlineStr">
         <is>
           <t>d026b17f-948b-4d7e-aeb1-e5f6517e00b6</t>
@@ -7319,6 +7379,11 @@
           <t>hhhhmmL h m m</t>
         </is>
       </c>
+      <c r="P132" t="inlineStr">
+        <is>
+          <t>fcba9322-2509-43aa-bc78-28a39ed93851</t>
+        </is>
+      </c>
       <c r="Q132" t="inlineStr">
         <is>
           <t>fcba9322-2509-43aa-bc78-28a39ed93851</t>
@@ -7351,6 +7416,11 @@
           <t>hhhhmmLLm!</t>
         </is>
       </c>
+      <c r="P133" t="inlineStr">
+        <is>
+          <t>9b2b685a-64cd-4fba-a32a-f187bd907299</t>
+        </is>
+      </c>
       <c r="Q133" t="inlineStr">
         <is>
           <t>9b2b685a-64cd-4fba-a32a-f187bd907299</t>
@@ -7383,6 +7453,11 @@
           <t>hhmhlhhmmm</t>
         </is>
       </c>
+      <c r="P134" t="inlineStr">
+        <is>
+          <t>1ba3e693-7890-4ba8-a3db-6fcafa95de8f</t>
+        </is>
+      </c>
       <c r="Q134" t="inlineStr">
         <is>
           <t>1ba3e693-7890-4ba8-a3db-6fcafa95de8f</t>
@@ -7415,6 +7490,11 @@
           <t>hhmmlmLm!</t>
         </is>
       </c>
+      <c r="P135" t="inlineStr">
+        <is>
+          <t>9a7af233-c051-469d-af17-0a10b3e720da</t>
+        </is>
+      </c>
       <c r="Q135" t="inlineStr">
         <is>
           <t>9a7af233-c051-469d-af17-0a10b3e720da</t>
@@ -7447,6 +7527,11 @@
           <t>hhmhlhhmm</t>
         </is>
       </c>
+      <c r="P136" t="inlineStr">
+        <is>
+          <t>3fcee715-1e4a-4a97-80c0-5fd0b0294be6</t>
+        </is>
+      </c>
       <c r="Q136" t="inlineStr">
         <is>
           <t>3fcee715-1e4a-4a97-80c0-5fd0b0294be6</t>
@@ -7479,6 +7564,11 @@
           <t>hhmhlhhmL</t>
         </is>
       </c>
+      <c r="P137" t="inlineStr">
+        <is>
+          <t>3966b0f8-bc0b-466d-83fd-f2a82202f8d9</t>
+        </is>
+      </c>
       <c r="Q137" t="inlineStr">
         <is>
           <t>3966b0f8-bc0b-466d-83fd-f2a82202f8d9</t>
@@ -7509,6 +7599,11 @@
       <c r="K138" t="inlineStr">
         <is>
           <t>hhmmm</t>
+        </is>
+      </c>
+      <c r="P138" t="inlineStr">
+        <is>
+          <t>73b74b43-c81d-45eb-972e-07cbd1c76456</t>
         </is>
       </c>
       <c r="Q138" t="inlineStr">

--- a/sources/jin_step6.xlsx
+++ b/sources/jin_step6.xlsx
@@ -843,6 +843,11 @@
           <t>– 1,2,1,2,1</t>
         </is>
       </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>1,2,1,1,2</t>
+        </is>
+      </c>
       <c r="C9" t="inlineStr">
         <is>
           <t>– Ultimate Punches</t>
@@ -888,6 +893,11 @@
       <c r="A10" t="inlineStr">
         <is>
           <t>– 2,1,2,1,2</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2,1,2,2,1</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
